--- a/embeds/data/education-care-realignment/slot-10-OECD-주요국-학생의-학업-관련-불안감,-2015.xlsx
+++ b/embeds/data/education-care-realignment/slot-10-OECD-주요국-학생의-학업-관련-불안감,-2015.xlsx
@@ -461,7 +461,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>시험을 잘 준비했더라도 불안하다 (%)</t>
+          <t>시험을 잘 준비했더라도 불안하다</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -484,7 +484,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>시험을 잘 준비했더라도 불안하다 (%)</t>
+          <t>시험을 잘 준비했더라도 불안하다</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -507,7 +507,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>시험을 잘 준비했더라도 불안하다 (%)</t>
+          <t>시험을 잘 준비했더라도 불안하다</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>시험을 잘 준비했더라도 불안하다 (%)</t>
+          <t>시험을 잘 준비했더라도 불안하다</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -553,7 +553,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>시험을 잘 준비했더라도 불안하다 (%)</t>
+          <t>시험을 잘 준비했더라도 불안하다</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -576,7 +576,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>시험을 잘 준비했더라도 불안하다 (%)</t>
+          <t>시험을 잘 준비했더라도 불안하다</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -599,7 +599,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>공부를 할 때 매우 긴장된다 (%)</t>
+          <t>공부를 할 때 매우 긴장된다</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -622,7 +622,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>공부를 할 때 매우 긴장된다 (%)</t>
+          <t>공부를 할 때 매우 긴장된다</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -645,7 +645,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>공부를 할 때 매우 긴장된다 (%)</t>
+          <t>공부를 할 때 매우 긴장된다</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -668,7 +668,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>공부를 할 때 매우 긴장된다 (%)</t>
+          <t>공부를 할 때 매우 긴장된다</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -691,7 +691,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>공부를 할 때 매우 긴장된다 (%)</t>
+          <t>공부를 할 때 매우 긴장된다</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -714,7 +714,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>공부를 할 때 매우 긴장된다 (%)</t>
+          <t>공부를 할 때 매우 긴장된다</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -737,7 +737,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>학업 관련 불안감 지수 (점)</t>
+          <t>학업 관련 불안감 지수</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -760,7 +760,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>학업 관련 불안감 지수 (점)</t>
+          <t>학업 관련 불안감 지수</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -783,7 +783,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>학업 관련 불안감 지수 (점)</t>
+          <t>학업 관련 불안감 지수</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -806,7 +806,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>학업 관련 불안감 지수 (점)</t>
+          <t>학업 관련 불안감 지수</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -829,7 +829,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>학업 관련 불안감 지수 (점)</t>
+          <t>학업 관련 불안감 지수</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -852,7 +852,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>학업 관련 불안감 지수 (점)</t>
+          <t>학업 관련 불안감 지수</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
